--- a/data/zh-cn/talents.xlsx
+++ b/data/zh-cn/talents.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiayuankevinguo/Desktop/life-final/data/zh-cn/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE4B5CA-1321-694E-8894-133A5966446E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FD48A9-BC21-1B4D-9FE5-3A086A2AFC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="talents" sheetId="1" r:id="rId1"/>
@@ -221,7 +221,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="794">
   <si>
     <t>序号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2872,6 +2872,12 @@
   </si>
   <si>
     <t>我的一些......'真心'话</t>
+  </si>
+  <si>
+    <t>aaa</t>
+  </si>
+  <si>
+    <t>测试git</t>
   </si>
 </sst>
 </file>
@@ -3288,7 +3294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BJ275"/>
+  <dimension ref="A1:BJ276"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="25.5" defaultRowHeight="39.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.5" style="1"/>
@@ -10571,6 +10577,20 @@
         <v>4</v>
       </c>
     </row>
+    <row r="276" spans="1:59" ht="39.75" customHeight="1">
+      <c r="A276" s="1">
+        <v>3098</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="E276" s="1">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/zh-cn/talents.xlsx
+++ b/data/zh-cn/talents.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiayuankevinguo/Desktop/life-final/data/zh-cn/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FD48A9-BC21-1B4D-9FE5-3A086A2AFC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C72C0C-F654-7940-8EAC-1226BC4EC0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -221,7 +221,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="792">
   <si>
     <t>序号</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2872,12 +2872,6 @@
   </si>
   <si>
     <t>我的一些......'真心'话</t>
-  </si>
-  <si>
-    <t>aaa</t>
-  </si>
-  <si>
-    <t>测试git</t>
   </si>
 </sst>
 </file>
@@ -3294,7 +3288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BJ276"/>
+  <dimension ref="A1:BJ275"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="25.5" defaultRowHeight="39.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.5" style="1"/>
@@ -10577,20 +10571,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:59" ht="39.75" customHeight="1">
-      <c r="A276" s="1">
-        <v>3098</v>
-      </c>
-      <c r="B276" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="C276" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="E276" s="1">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
